--- a/schoolDocs/StudentImportData/LKG_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/LKG_ImportReady.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="65">
   <si>
     <t>Sr No</t>
   </si>
@@ -95,7 +95,7 @@
     <t>discount</t>
   </si>
   <si>
-    <t>27/01/2024</t>
+    <t>05/01/2024</t>
   </si>
   <si>
     <t>Wakdapul</t>
@@ -110,13 +110,13 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>Discount 75% on girls fee ₹12200 = ₹3050 payable</t>
+    <t>Discount 75% on girls fee ₹12200 = ₹3050</t>
   </si>
   <si>
     <t>Swamini Rajesh Karde</t>
   </si>
   <si>
-    <t>31/12/2024</t>
+    <t>31/01/2024</t>
   </si>
   <si>
     <t>Kedgaon</t>
@@ -131,7 +131,7 @@
     <t>Service</t>
   </si>
   <si>
-    <t>Discount 25% on girls fee ₹12200 = ₹9150 payable</t>
+    <t>Discount 25% on girls fee ₹12200 = ₹9150</t>
   </si>
   <si>
     <t>Rashmika Mahendra Paithanpagere</t>
@@ -140,7 +140,7 @@
     <t>general</t>
   </si>
   <si>
-    <t>11/02/2024</t>
+    <t>31/12/2023</t>
   </si>
   <si>
     <t>Tulevasti</t>
@@ -149,13 +149,10 @@
     <t>700metre</t>
   </si>
   <si>
-    <t>Partial payment — ₹9000 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Swaranjali Sagar Tule</t>
   </si>
   <si>
-    <t>15/02/2024</t>
+    <t>04/02/2024</t>
   </si>
   <si>
     <t>Kesskervasti</t>
@@ -167,16 +164,13 @@
     <t>Driver</t>
   </si>
   <si>
-    <t>Partial payment — ₹4067 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Gayatri Bharat Jadhav</t>
   </si>
   <si>
     <t>rte</t>
   </si>
   <si>
-    <t>17/01/2024</t>
+    <t>08/02/2024</t>
   </si>
   <si>
     <t>Cahaufula</t>
@@ -191,7 +185,7 @@
     <t>Savi Deepak Lonkar</t>
   </si>
   <si>
-    <t>29/12/2023</t>
+    <t>10/02/2024</t>
   </si>
   <si>
     <t>Boripardhi</t>
@@ -203,16 +197,16 @@
     <t>Kshitija Khanderao Devkar</t>
   </si>
   <si>
-    <t>25/01/2024</t>
-  </si>
-  <si>
-    <t>DGA sheet had 200 in discount col — treated as General. Please verify fee category.</t>
+    <t>23/01/2024</t>
+  </si>
+  <si>
+    <t>DGA sheet had 200 in discount col — treated as General. Please verify.</t>
   </si>
   <si>
     <t>Dhanashree C Kokare</t>
   </si>
   <si>
-    <t>20/12/2023</t>
+    <t>07/02/2025</t>
   </si>
   <si>
     <t>Shepherd</t>
@@ -613,27 +607,27 @@
   <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="37.705" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="98.976" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="37.705" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.569" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="23.423" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="83.694" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -726,6 +720,7 @@
       <c r="I2">
         <v>75</v>
       </c>
+      <c r="J2"/>
       <c r="K2">
         <v>3050</v>
       </c>
@@ -773,6 +768,7 @@
       <c r="I3">
         <v>25</v>
       </c>
+      <c r="J3"/>
       <c r="K3">
         <v>9150</v>
       </c>
@@ -817,8 +813,10 @@
       <c r="H4" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="5">
-        <v>9000</v>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4">
+        <v>12200</v>
       </c>
       <c r="L4" t="s">
         <v>41</v>
@@ -834,9 +832,6 @@
       </c>
       <c r="R4" t="s">
         <v>30</v>
-      </c>
-      <c r="U4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -844,7 +839,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -861,26 +856,25 @@
       <c r="H5" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="5">
-        <v>4067</v>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5">
+        <v>12200</v>
       </c>
       <c r="L5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" t="s">
         <v>46</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>47</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
         <v>48</v>
-      </c>
-      <c r="P5" t="s">
-        <v>49</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
-      </c>
-      <c r="U5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -888,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -903,25 +897,30 @@
         <v>8799964616</v>
       </c>
       <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6" t="s">
         <v>52</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>53</v>
       </c>
-      <c r="M6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" t="s">
-        <v>55</v>
-      </c>
       <c r="P6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
       <c r="U6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -929,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -946,20 +945,22 @@
       <c r="H7" t="s">
         <v>40</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7">
         <v>12200</v>
       </c>
       <c r="L7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N7" t="s">
         <v>35</v>
       </c>
       <c r="P7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
@@ -970,7 +971,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -984,11 +985,13 @@
       <c r="H8" t="s">
         <v>40</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
       <c r="K8">
         <v>12200</v>
       </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M8" t="s">
         <v>34</v>
@@ -1000,7 +1003,7 @@
         <v>30</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1008,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1025,17 +1028,22 @@
       <c r="H9" t="s">
         <v>40</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9">
+        <v>12200</v>
+      </c>
       <c r="L9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>

--- a/schoolDocs/StudentImportData/LKG_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/LKG_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Vedika Kiran Zamadar</t>
@@ -110,9 +136,6 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>Discount 75% on girls fee ₹12200 = ₹3050</t>
-  </si>
-  <si>
     <t>Swamini Rajesh Karde</t>
   </si>
   <si>
@@ -131,9 +154,6 @@
     <t>Service</t>
   </si>
   <si>
-    <t>Discount 25% on girls fee ₹12200 = ₹9150</t>
-  </si>
-  <si>
     <t>Rashmika Mahendra Paithanpagere</t>
   </si>
   <si>
@@ -179,7 +199,7 @@
     <t>1.5km</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000002</t>
   </si>
   <si>
     <t>Savi Deepak Lonkar</t>
@@ -198,9 +218,6 @@
   </si>
   <si>
     <t>23/01/2024</t>
-  </si>
-  <si>
-    <t>DGA sheet had 200 in discount col — treated as General. Please verify.</t>
   </si>
   <si>
     <t>Dhanashree C Kokare</t>
@@ -261,12 +278,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -274,6 +285,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -295,16 +312,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,7 +644,7 @@
     <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="83.694" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -661,10 +678,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -691,7 +708,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -739,16 +756,14 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
-      <c r="U2" t="s">
-        <v>31</v>
-      </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -773,30 +788,28 @@
         <v>9150</v>
       </c>
       <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
         <v>33</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>35</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>36</v>
       </c>
-      <c r="R3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" t="s">
-        <v>38</v>
-      </c>
+      <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -811,7 +824,7 @@
         <v>8692918582</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
@@ -819,13 +832,13 @@
         <v>12200</v>
       </c>
       <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" t="s">
         <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
       </c>
       <c r="P4" t="s">
         <v>29</v>
@@ -833,13 +846,14 @@
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -854,7 +868,7 @@
         <v>7040765469</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -862,27 +876,28 @@
         <v>12200</v>
       </c>
       <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s">
         <v>45</v>
       </c>
-      <c r="M5" t="s">
+      <c r="P5" t="s">
         <v>46</v>
-      </c>
-      <c r="N5" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" t="s">
-        <v>48</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -897,7 +912,7 @@
         <v>8799964616</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -905,22 +920,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
         <v>51</v>
       </c>
-      <c r="M6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" t="s">
-        <v>53</v>
-      </c>
       <c r="P6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
       <c r="U6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -928,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -943,7 +958,7 @@
         <v>9604649125</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -951,27 +966,28 @@
         <v>12200</v>
       </c>
       <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" t="s">
         <v>56</v>
-      </c>
-      <c r="M7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" t="s">
-        <v>58</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -983,7 +999,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -991,27 +1007,25 @@
         <v>12200</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" t="s">
         <v>34</v>
-      </c>
-      <c r="N8" t="s">
-        <v>35</v>
       </c>
       <c r="R8" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="U8" s="4"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1026,7 +1040,7 @@
         <v>8830152900</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1034,20 +1048,21 @@
         <v>12200</v>
       </c>
       <c r="L9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
+      <c r="U9"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -1061,6 +1076,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>